--- a/assets/translations/German.Germany.de-DE.xlsx
+++ b/assets/translations/German.Germany.de-DE.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11130"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/zauner/Documents/Arbeit/12-TUM/Repos_Misc/2024-04_Ladenburg_Roundtable/LCS/assets/translations/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DCB07CD3-E1DF-9F46-B58A-CABF630360BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{68159958-950A-1447-864E-35F8F46AF9A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1220" yWindow="680" windowWidth="25020" windowHeight="21660" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -545,9 +545,6 @@
     <t>Über die  intrinsisch lichtempfindlichen retinalen Ganglienzellen (ipRGC) bewirkt Licht die Unterdrückung von Melatonin am Abend und in der Nacht.</t>
   </si>
   <si>
-    <t>Licht ist das Hauptsignal, das sicherstellt, dass der Körper mit dem 24-Stunden Hell-Dunkel-Rhytmus der Umgebung in Einklang bleibt.</t>
-  </si>
-  <si>
     <t>Licht beeinflusst direkt die biologische Uhr im Gehirn und reguliert sowohl den Schlaf-Wach-Rhythmus als auch andere tägliche physiologische Rhythmen.</t>
   </si>
   <si>
@@ -756,6 +753,9 @@
   </si>
   <si>
     <t>Gemeinsame Stellungnahme</t>
+  </si>
+  <si>
+    <t>Licht ist das Hauptsignal, das sicherstellt, dass der Körper mit dem 24-Stunden Hell-Dunkel-Rhythmus der Umgebung in Einklang bleibt.</t>
   </si>
 </sst>
 </file>
@@ -1055,8 +1055,8 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -29418,19 +29418,19 @@
         <v>10</v>
       </c>
       <c r="F1" s="21" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="G1" s="6" t="s">
         <v>11</v>
       </c>
       <c r="H1" s="21" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="I1" s="6" t="s">
         <v>12</v>
       </c>
       <c r="J1" s="21" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
     </row>
     <row r="2" spans="1:27" ht="136" x14ac:dyDescent="0.2">
@@ -29456,13 +29456,13 @@
         <v>15</v>
       </c>
       <c r="H2" s="21" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="I2" s="9" t="s">
         <v>16</v>
       </c>
       <c r="J2" s="21" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="K2" s="10"/>
       <c r="L2" s="10"/>
@@ -29482,7 +29482,7 @@
       <c r="Z2" s="10"/>
       <c r="AA2" s="10"/>
     </row>
-    <row r="3" spans="1:27" ht="136" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:27" ht="119" x14ac:dyDescent="0.2">
       <c r="A3" s="7" t="s">
         <v>13</v>
       </c>
@@ -29505,13 +29505,13 @@
         <v>18</v>
       </c>
       <c r="H3" s="21" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="I3" s="9" t="s">
         <v>19</v>
       </c>
       <c r="J3" s="21" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
     </row>
     <row r="4" spans="1:27" ht="170" x14ac:dyDescent="0.2">
@@ -29537,13 +29537,13 @@
         <v>21</v>
       </c>
       <c r="H4" s="21" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="I4" s="9" t="s">
         <v>22</v>
       </c>
       <c r="J4" s="21" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
     <row r="5" spans="1:27" ht="204" x14ac:dyDescent="0.2">
@@ -29569,13 +29569,13 @@
         <v>24</v>
       </c>
       <c r="H5" s="21" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="I5" s="9" t="s">
         <v>25</v>
       </c>
       <c r="J5" s="21" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
     </row>
     <row r="6" spans="1:27" ht="170" x14ac:dyDescent="0.2">
@@ -29601,13 +29601,13 @@
         <v>27</v>
       </c>
       <c r="H6" s="21" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="I6" s="9" t="s">
         <v>28</v>
       </c>
       <c r="J6" s="21" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
     <row r="7" spans="1:27" ht="136" x14ac:dyDescent="0.2">
@@ -29633,13 +29633,13 @@
         <v>30</v>
       </c>
       <c r="H7" s="21" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="I7" s="9" t="s">
         <v>31</v>
       </c>
       <c r="J7" s="21" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
     </row>
     <row r="8" spans="1:27" ht="136" x14ac:dyDescent="0.2">
@@ -29665,13 +29665,13 @@
         <v>34</v>
       </c>
       <c r="H8" s="21" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="I8" s="15" t="s">
         <v>101</v>
       </c>
       <c r="J8" s="21" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
     </row>
     <row r="9" spans="1:27" ht="119" x14ac:dyDescent="0.2">
@@ -29697,13 +29697,13 @@
         <v>36</v>
       </c>
       <c r="H9" s="21" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="I9" s="9" t="s">
         <v>37</v>
       </c>
       <c r="J9" s="21" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
     </row>
     <row r="10" spans="1:27" ht="85" x14ac:dyDescent="0.2">
@@ -29729,16 +29729,16 @@
         <v>39</v>
       </c>
       <c r="H10" s="21" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="I10" s="9" t="s">
         <v>40</v>
       </c>
       <c r="J10" s="21" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="11" spans="1:27" ht="119" x14ac:dyDescent="0.2">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="11" spans="1:27" ht="102" x14ac:dyDescent="0.2">
       <c r="A11" s="7" t="s">
         <v>41</v>
       </c>
@@ -29761,13 +29761,13 @@
         <v>43</v>
       </c>
       <c r="H11" s="21" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="I11" s="9" t="s">
         <v>44</v>
       </c>
       <c r="J11" s="21" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
     </row>
     <row r="12" spans="1:27" ht="153" x14ac:dyDescent="0.2">
@@ -29793,13 +29793,13 @@
         <v>46</v>
       </c>
       <c r="H12" s="21" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="I12" s="9" t="s">
         <v>47</v>
       </c>
       <c r="J12" s="21" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="13" spans="1:27" ht="102" x14ac:dyDescent="0.2">
@@ -29819,19 +29819,19 @@
         <v>48</v>
       </c>
       <c r="F13" s="21" t="s">
-        <v>165</v>
+        <v>235</v>
       </c>
       <c r="G13" s="9" t="s">
         <v>49</v>
       </c>
       <c r="H13" s="21" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="I13" s="9" t="s">
         <v>50</v>
       </c>
       <c r="J13" s="21" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
     <row r="14" spans="1:27" ht="102" x14ac:dyDescent="0.2">
@@ -29851,19 +29851,19 @@
         <v>51</v>
       </c>
       <c r="F14" s="21" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="G14" s="9" t="s">
         <v>52</v>
       </c>
       <c r="H14" s="21" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="I14" s="9" t="s">
         <v>53</v>
       </c>
       <c r="J14" s="21" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
     </row>
     <row r="15" spans="1:27" ht="119" x14ac:dyDescent="0.2">
@@ -29883,19 +29883,19 @@
         <v>54</v>
       </c>
       <c r="F15" s="21" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="G15" s="9" t="s">
         <v>55</v>
       </c>
       <c r="H15" s="21" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="I15" s="9" t="s">
         <v>56</v>
       </c>
       <c r="J15" s="21" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
     </row>
     <row r="16" spans="1:27" ht="102" x14ac:dyDescent="0.2">
@@ -29915,19 +29915,19 @@
         <v>57</v>
       </c>
       <c r="F16" s="21" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="G16" s="9" t="s">
         <v>58</v>
       </c>
       <c r="H16" s="21" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="I16" s="9" t="s">
         <v>59</v>
       </c>
       <c r="J16" s="21" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
     </row>
     <row r="17" spans="1:10" ht="170" x14ac:dyDescent="0.2">
@@ -29947,19 +29947,19 @@
         <v>60</v>
       </c>
       <c r="F17" s="21" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="G17" s="9" t="s">
         <v>61</v>
       </c>
       <c r="H17" s="21" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="I17" s="9" t="s">
         <v>62</v>
       </c>
       <c r="J17" s="21" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
     </row>
     <row r="18" spans="1:10" ht="68" x14ac:dyDescent="0.2">
@@ -29979,19 +29979,19 @@
         <v>63</v>
       </c>
       <c r="F18" s="21" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="G18" s="9" t="s">
         <v>64</v>
       </c>
       <c r="H18" s="21" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="I18" s="15" t="s">
         <v>65</v>
       </c>
       <c r="J18" s="21" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
     </row>
     <row r="19" spans="1:10" ht="119" x14ac:dyDescent="0.2">
@@ -30011,19 +30011,19 @@
         <v>66</v>
       </c>
       <c r="F19" s="21" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="G19" s="9" t="s">
         <v>67</v>
       </c>
       <c r="H19" s="21" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="I19" s="9" t="s">
         <v>68</v>
       </c>
       <c r="J19" s="21" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
     </row>
     <row r="20" spans="1:10" ht="85" x14ac:dyDescent="0.2">
@@ -30043,19 +30043,19 @@
         <v>69</v>
       </c>
       <c r="F20" s="21" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="G20" s="9" t="s">
         <v>70</v>
       </c>
       <c r="H20" s="21" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="I20" s="9" t="s">
         <v>71</v>
       </c>
       <c r="J20" s="21" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
     </row>
     <row r="21" spans="1:10" ht="153" x14ac:dyDescent="0.2">
@@ -30075,19 +30075,19 @@
         <v>72</v>
       </c>
       <c r="F21" s="21" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="G21" s="9" t="s">
         <v>73</v>
       </c>
       <c r="H21" s="21" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="I21" s="9" t="s">
         <v>74</v>
       </c>
       <c r="J21" s="21" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
     </row>
     <row r="22" spans="1:10" ht="102" x14ac:dyDescent="0.2">
@@ -30107,19 +30107,19 @@
         <v>76</v>
       </c>
       <c r="F22" s="21" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="G22" s="9" t="s">
         <v>77</v>
       </c>
       <c r="H22" s="21" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="I22" s="9" t="s">
         <v>78</v>
       </c>
       <c r="J22" s="21" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
     </row>
     <row r="23" spans="1:10" ht="136" x14ac:dyDescent="0.2">
@@ -30139,19 +30139,19 @@
         <v>79</v>
       </c>
       <c r="F23" s="21" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="G23" s="9" t="s">
         <v>80</v>
       </c>
       <c r="H23" s="21" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="I23" s="9" t="s">
         <v>81</v>
       </c>
       <c r="J23" s="21" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
     </row>
     <row r="24" spans="1:10" ht="68" x14ac:dyDescent="0.2">
@@ -30171,19 +30171,19 @@
         <v>82</v>
       </c>
       <c r="F24" s="21" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="G24" s="9" t="s">
         <v>83</v>
       </c>
       <c r="H24" s="21" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="I24" s="9" t="s">
         <v>84</v>
       </c>
       <c r="J24" s="21" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
     </row>
     <row r="25" spans="1:10" ht="85" x14ac:dyDescent="0.2">
@@ -30203,19 +30203,19 @@
         <v>86</v>
       </c>
       <c r="F25" s="21" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="G25" s="9" t="s">
         <v>87</v>
       </c>
       <c r="H25" s="21" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="I25" s="9" t="s">
         <v>88</v>
       </c>
       <c r="J25" s="21" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
     </row>
     <row r="26" spans="1:10" ht="187" x14ac:dyDescent="0.2">
@@ -30235,19 +30235,19 @@
         <v>89</v>
       </c>
       <c r="F26" s="21" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="G26" s="9" t="s">
         <v>90</v>
       </c>
       <c r="H26" s="21" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="I26" s="9" t="s">
         <v>91</v>
       </c>
       <c r="J26" s="21" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
     </row>
     <row r="27" spans="1:10" ht="170" x14ac:dyDescent="0.2">
@@ -30267,19 +30267,19 @@
         <v>92</v>
       </c>
       <c r="F27" s="21" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="G27" s="13" t="s">
         <v>93</v>
       </c>
       <c r="H27" s="21" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="I27" s="13" t="s">
         <v>94</v>
       </c>
       <c r="J27" s="21" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
     </row>
   </sheetData>
@@ -31375,7 +31375,7 @@
         <v>142</v>
       </c>
       <c r="B2" s="19" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.2">
